--- a/05. Res/modelos/coeficientes_gamma.xlsx
+++ b/05. Res/modelos/coeficientes_gamma.xlsx
@@ -466,16 +466,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>5.37965934248082</v>
+        <v>5.39772221062641</v>
       </c>
       <c r="C2" t="n">
-        <v>0.291535977481544</v>
+        <v>0.290612373787534</v>
       </c>
       <c r="D2" t="n">
-        <v>18.4528146026896</v>
+        <v>18.573614537737</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000313288250185832</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000346444161823771</v>
       </c>
     </row>
     <row r="3">
@@ -483,16 +483,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0232865429922336</v>
+        <v>-0.0248238409390034</v>
       </c>
       <c r="C3" t="n">
-        <v>0.189614179489802</v>
+        <v>0.18316175061736</v>
       </c>
       <c r="D3" t="n">
-        <v>0.122810135058945</v>
+        <v>-0.13552961169749</v>
       </c>
       <c r="E3" t="n">
-        <v>0.902259032962569</v>
+        <v>0.892194898002048</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>0.175427904673791</v>
+        <v>0.139856818130456</v>
       </c>
       <c r="C4" t="n">
-        <v>0.175615748237861</v>
+        <v>0.169655697073842</v>
       </c>
       <c r="D4" t="n">
-        <v>0.998930371757915</v>
+        <v>0.824356744528203</v>
       </c>
       <c r="E4" t="n">
-        <v>0.317843941109764</v>
+        <v>0.409749458828372</v>
       </c>
     </row>
     <row r="5">
@@ -517,16 +517,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.896343889223192</v>
+        <v>-0.992685271782836</v>
       </c>
       <c r="C5" t="n">
-        <v>3.55920692050235</v>
+        <v>3.47208394066662</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.251838094621563</v>
+        <v>-0.285904744455069</v>
       </c>
       <c r="E5" t="n">
-        <v>0.801169533606425</v>
+        <v>0.774954867010699</v>
       </c>
     </row>
     <row r="6">
@@ -534,16 +534,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0249173817284482</v>
+        <v>-0.0616415073678273</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0633097944669356</v>
+        <v>0.0615068943962351</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.393578622995872</v>
+        <v>-1.00218858345741</v>
       </c>
       <c r="E6" t="n">
-        <v>0.693897553865353</v>
+        <v>0.316268028450602</v>
       </c>
     </row>
     <row r="7">
@@ -551,16 +551,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>0.357070066373767</v>
+        <v>0.502733128401282</v>
       </c>
       <c r="C7" t="n">
-        <v>0.230935799147374</v>
+        <v>0.22753258789315</v>
       </c>
       <c r="D7" t="n">
-        <v>1.54618758846435</v>
+        <v>2.20949945261189</v>
       </c>
       <c r="E7" t="n">
-        <v>0.122079587388374</v>
+        <v>0.0271543575176545</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>0.41051128369185</v>
+        <v>0.547135612259803</v>
       </c>
       <c r="C8" t="n">
-        <v>0.236252256076236</v>
+        <v>0.233266615624323</v>
       </c>
       <c r="D8" t="n">
-        <v>1.73759730598882</v>
+        <v>2.34553757637127</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0823015611607504</v>
+        <v>0.0190120908860441</v>
       </c>
     </row>
     <row r="9">
@@ -585,16 +585,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>0.402291912274346</v>
+        <v>0.541574531753584</v>
       </c>
       <c r="C9" t="n">
-        <v>0.244693554535516</v>
+        <v>0.241204841442523</v>
       </c>
       <c r="D9" t="n">
-        <v>1.64406419710559</v>
+        <v>2.24528881142975</v>
       </c>
       <c r="E9" t="n">
-        <v>0.100183125103869</v>
+        <v>0.0247635119628836</v>
       </c>
     </row>
     <row r="10">
@@ -602,16 +602,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>0.415385124213592</v>
+        <v>0.536442007695213</v>
       </c>
       <c r="C10" t="n">
-        <v>0.251193799989943</v>
+        <v>0.247680412697993</v>
       </c>
       <c r="D10" t="n">
-        <v>1.65364401601561</v>
+        <v>2.16586367025042</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0982200164155472</v>
+        <v>0.0303366701677462</v>
       </c>
     </row>
     <row r="11">
@@ -619,16 +619,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>0.410084078476658</v>
+        <v>0.554221207883027</v>
       </c>
       <c r="C11" t="n">
-        <v>0.265425349706295</v>
+        <v>0.260472863857949</v>
       </c>
       <c r="D11" t="n">
-        <v>1.54500720797932</v>
+        <v>2.12775027568813</v>
       </c>
       <c r="E11" t="n">
-        <v>0.122364836831354</v>
+        <v>0.033373392802462</v>
       </c>
     </row>
     <row r="12">
@@ -636,16 +636,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>0.179647285512716</v>
+        <v>0.0788470628720795</v>
       </c>
       <c r="C12" t="n">
-        <v>0.286520064536656</v>
+        <v>0.286105556511157</v>
       </c>
       <c r="D12" t="n">
-        <v>0.626997225493548</v>
+        <v>0.275587317609488</v>
       </c>
       <c r="E12" t="n">
-        <v>0.53067024430271</v>
+        <v>0.782868693182432</v>
       </c>
     </row>
     <row r="13">
@@ -653,16 +653,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0977491016923244</v>
+        <v>-0.206483654431345</v>
       </c>
       <c r="C13" t="n">
-        <v>0.273312916896137</v>
+        <v>0.27318556044551</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.357645378792948</v>
+        <v>-0.7558366338785</v>
       </c>
       <c r="E13" t="n">
-        <v>0.720613560311494</v>
+        <v>0.449758535009614</v>
       </c>
     </row>
     <row r="14">
@@ -670,16 +670,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.149717362146624</v>
+        <v>-0.251869613707798</v>
       </c>
       <c r="C14" t="n">
-        <v>0.272465393059369</v>
+        <v>0.272563798640606</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.549491296731402</v>
+        <v>-0.924075812576654</v>
       </c>
       <c r="E14" t="n">
-        <v>0.582676214022432</v>
+        <v>0.355461104549585</v>
       </c>
     </row>
     <row r="15">
@@ -687,16 +687,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.257877323537579</v>
+        <v>-0.373297504547102</v>
       </c>
       <c r="C15" t="n">
-        <v>0.279837182817333</v>
+        <v>0.279725788373624</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.921526299476474</v>
+        <v>-1.33451229762376</v>
       </c>
       <c r="E15" t="n">
-        <v>0.35678999065665</v>
+        <v>0.182055450893252</v>
       </c>
     </row>
     <row r="16">
@@ -704,16 +704,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.00345038539741163</v>
+        <v>-0.00277812908805455</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0870307429560992</v>
+        <v>0.0838176826201008</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0396455928125548</v>
+        <v>-0.0331449045262475</v>
       </c>
       <c r="E16" t="n">
-        <v>0.968376186324903</v>
+        <v>0.973559456808188</v>
       </c>
     </row>
     <row r="17">
@@ -721,16 +721,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.0613963561795221</v>
+        <v>-0.0763728447758969</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0947775933031783</v>
+        <v>0.0912763779936684</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.647793998979537</v>
+        <v>-0.836720808325618</v>
       </c>
       <c r="E17" t="n">
-        <v>0.517127745842746</v>
+        <v>0.402762306437469</v>
       </c>
     </row>
     <row r="18">
@@ -738,16 +738,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0857756316439934</v>
+        <v>0.0343326374692927</v>
       </c>
       <c r="C18" t="n">
-        <v>0.178965691367341</v>
+        <v>0.174182704253051</v>
       </c>
       <c r="D18" t="n">
-        <v>0.479285336695804</v>
+        <v>0.197107041233063</v>
       </c>
       <c r="E18" t="n">
-        <v>0.631742381477525</v>
+        <v>0.843746335195697</v>
       </c>
     </row>
     <row r="19">
@@ -755,16 +755,16 @@
         <v>22</v>
       </c>
       <c r="B19" t="n">
-        <v>0.181582684694698</v>
+        <v>0.156043332919692</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0975940289419114</v>
+        <v>0.0939584551818648</v>
       </c>
       <c r="D19" t="n">
-        <v>1.86059215572273</v>
+        <v>1.66076946047757</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0628206254911464</v>
+        <v>0.0967798054347264</v>
       </c>
     </row>
     <row r="20">
@@ -772,16 +772,16 @@
         <v>23</v>
       </c>
       <c r="B20" t="n">
-        <v>0.188901163781747</v>
+        <v>0.174967232130399</v>
       </c>
       <c r="C20" t="n">
-        <v>0.106489757739606</v>
+        <v>0.102568128999739</v>
       </c>
       <c r="D20" t="n">
-        <v>1.77389044534834</v>
+        <v>1.70586354491115</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0761008073014202</v>
+        <v>0.0880533473009023</v>
       </c>
     </row>
     <row r="21">
@@ -789,16 +789,16 @@
         <v>24</v>
       </c>
       <c r="B21" t="n">
-        <v>0.181100621409855</v>
+        <v>0.19602283611747</v>
       </c>
       <c r="C21" t="n">
-        <v>0.113986798719581</v>
+        <v>0.110067489336312</v>
       </c>
       <c r="D21" t="n">
-        <v>1.58878592472256</v>
+        <v>1.78093311021677</v>
       </c>
       <c r="E21" t="n">
-        <v>0.112129029772982</v>
+        <v>0.0749427859001271</v>
       </c>
     </row>
     <row r="22">
@@ -806,16 +806,16 @@
         <v>25</v>
       </c>
       <c r="B22" t="n">
-        <v>0.00712081117618372</v>
+        <v>0.036461408557713</v>
       </c>
       <c r="C22" t="n">
-        <v>0.059907447094532</v>
+        <v>0.0581658472524923</v>
       </c>
       <c r="D22" t="n">
-        <v>0.118863539034593</v>
+        <v>0.626852530823415</v>
       </c>
       <c r="E22" t="n">
-        <v>0.905385001483649</v>
+        <v>0.530765057319212</v>
       </c>
     </row>
     <row r="23">
@@ -823,16 +823,16 @@
         <v>26</v>
       </c>
       <c r="B23" t="n">
-        <v>0.00118253772358278</v>
+        <v>0.00127219930616493</v>
       </c>
       <c r="C23" t="n">
-        <v>0.000208372878593648</v>
+        <v>0.000201705160131276</v>
       </c>
       <c r="D23" t="n">
-        <v>5.67510384059562</v>
+        <v>6.30722240986273</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0000000141072193268114</v>
+        <v>0.000000000291720898532058</v>
       </c>
     </row>
     <row r="24">
@@ -840,16 +840,16 @@
         <v>27</v>
       </c>
       <c r="B24" t="n">
-        <v>0.000196862236080984</v>
+        <v>-0.00580420341539169</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00743661323945036</v>
+        <v>0.00715091761403764</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0264720282932898</v>
+        <v>-0.811672533326034</v>
       </c>
       <c r="E24" t="n">
-        <v>0.978881183113099</v>
+        <v>0.416991913831588</v>
       </c>
     </row>
     <row r="25">
@@ -857,16 +857,16 @@
         <v>28</v>
       </c>
       <c r="B25" t="n">
-        <v>0.294172570127677</v>
+        <v>0.297725059960922</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0330539384271158</v>
+        <v>0.0313001007409867</v>
       </c>
       <c r="D25" t="n">
-        <v>8.89977364653021</v>
+        <v>9.51195213154885</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000000000000000000620245811269043</v>
+        <v>0.00000000000000000000213787458961253</v>
       </c>
     </row>
     <row r="26">
@@ -874,16 +874,16 @@
         <v>29</v>
       </c>
       <c r="B26" t="n">
-        <v>0.00337840511346171</v>
+        <v>0.00255001054421514</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00689542347743483</v>
+        <v>0.00666831444327923</v>
       </c>
       <c r="D26" t="n">
-        <v>0.489948895019645</v>
+        <v>0.382407063419933</v>
       </c>
       <c r="E26" t="n">
-        <v>0.62417696342788</v>
+        <v>0.70216464912539</v>
       </c>
     </row>
   </sheetData>
